--- a/rsvp_forms/006_how_to_be_successful_as_a_ceo_with_multiple_busineses--rsvp_forms.xlsx
+++ b/rsvp_forms/006_how_to_be_successful_as_a_ceo_with_multiple_busineses--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>how_to_be_successful_as_a_ceo_with_multiple_busineses</t>
+          <t>How To Be Successful As A Ceo With Multiple Businesses</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,10 +548,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Briefly describe yourself</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,17 +565,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>rsvp_form_title</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>RSVP Form Title</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +588,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rsvp_forms</t>
+          <t>rsvp_do_you_feel_overwhelmed_at_times</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rsvp_forms</t>
+          <t>Do You Feel Overwhelmed At Times?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>do_you_feel_overwhelmed_at_times</t>
+          <t>rsvp_do_you_use_time_blocks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>do_you_feel_overwhelmed_at_times</t>
+          <t>Do You Use Time Blocks?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>do_you_use_time_blocks</t>
+          <t>rsvp_do_you_feel_stress_prophets_stresses</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time_blocks</t>
+          <t>How Do You Feel About Stress?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>do_you_feel_stress_prophets_stresses</t>
+          <t>rsvp_successful_with_multiple_businesses</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stresses</t>
+          <t>How to Be Successful with Multiple Businesses</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>do_you_feel_stress_with_much_stress</t>
+          <t>rsvp_form</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>much_stress</t>
+          <t>RSVP Form</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,20 +703,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses</t>
+          <t>rsvp_output_file</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>successful_with_multiple_businesses</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Output File</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter the output file name</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,17 +730,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_stress_free</t>
+          <t>rsvp_form_id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>stress_free</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +758,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_stress_free_why</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>why</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +776,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rsvp</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rsvp</t>
+          <t>Form Description 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +804,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>rsvp_form_output</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rsvp_forms</t>
+          <t>RSVP Form Output</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +827,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>rsvp_form_id_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Rsvp Form Id 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +850,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>successful_with_multiple_businesses_why</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Why Be Successful with Multiple Businesses</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +873,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_title_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form Title</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +896,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>rsvp_forms</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rsvp_forms</t>
+          <t>RSVP Forms</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +919,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rsvp_forms</t>
+          <t>Output File (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>rsvp_forms</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>rsvp_forms</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>rsvp_forms</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>rsvp_forms</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>rsvp_forms</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>rsvp_forms</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>rsvp_forms</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +945,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,272 +973,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>rsvp_do_you_feel_overwhelmed_at_times_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rsvp_forms</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RSVP Forms</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>rsvp_do_you_feel_overwhelmed_at_times_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>do_you_use_time_blocks_choices</t>
+          <t>rsvp_do_you_feel_overwhelmed_at_times_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>do_you_use_time_blocks_choices</t>
+          <t>rsvp_do_you_use_time_blocks_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>do_you_use_time_blocks_choices</t>
+          <t>rsvp_do_you_use_time_blocks_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_sure</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>not_sure</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>do_you_feel_stress_with_much_stress_choices</t>
+          <t>rsvp_do_you_use_time_blocks_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a_lot</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>a_lot</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>do_you_feel_stress_with_much_stress_choices</t>
+          <t>rsvp_do_you_feel_stress_prophets_stresses_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>little_stress</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>little_stress</t>
+          <t>A Lot</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_choices</t>
+          <t>rsvp_do_you_feel_stress_prophets_stresses_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sign_up_today</t>
+          <t>a_little</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sign_up_today</t>
+          <t>A Little</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_choices</t>
+          <t>rsvp_do_you_feel_stress_prophets_stresses_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_us_later</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_us_later</t>
+          <t>Not at All</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_choices</t>
+          <t>rsvp_successful_with_multiple_businesses_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>do_not_want_to_learn</t>
+          <t>sign_up_today</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>do_not_want_to_learn</t>
+          <t>Sign Up Today</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_stress_free_choices</t>
+          <t>rsvp_successful_with_multiple_businesses_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sign_up_today</t>
+          <t>contact_us_later</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sign_up_today</t>
+          <t>Contact Us Later</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_stress_free_choices</t>
+          <t>rsvp_successful_with_multiple_businesses_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_us_later</t>
+          <t>no_interest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_us_later</t>
+          <t>No Interest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>how_to_be_successful_with_multiple_businesses_stress_free_choices</t>
+          <t>rsvp_form_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>do_not_want_to_learn</t>
+          <t>rsvp_form_for_form_title</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>do_not_want_to_learn</t>
+          <t>RSVP Form for Form Title</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rsvp_choices</t>
+          <t>rsvp_form_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sign_up_today</t>
+          <t>another_rsvp_form</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sign_up_today</t>
+          <t>Another RSVP Form</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rsvp_choices</t>
+          <t>rsvp_form_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_us_later</t>
+          <t>no_rsvp_form</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_us_later</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>rsvp_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>do_not_want_to_learn</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>do_not_want_to_learn</t>
+          <t>No RSVP Form</t>
         </is>
       </c>
     </row>
